--- a/inquiry_forms/036_software_launch_user_inquiry_form--inquiry_forms.xlsx
+++ b/inquiry_forms/036_software_launch_user_inquiry_form--inquiry_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -939,7 +939,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Other (please specify)</t>
+          <t>Role Other</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -962,7 +962,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Launch Interest</t>
+          <t>Launch Interest Other</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -985,7 +985,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Other (please specify)</t>
+          <t>Job Function Other Description</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Other (please specify)</t>
+          <t>Role Other Description</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Other (please specify)</t>
+          <t>Company Size Other</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Other (please specify)</t>
+          <t>Company Size Other Description</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'software'}</t>
+          <t>software</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Software'}</t>
+          <t>Software</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'app'}</t>
+          <t>app</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'App'}</t>
+          <t>App</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'tool'}</t>
+          <t>tool</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Tool'}</t>
+          <t>Tool</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'platform'}</t>
+          <t>platform</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Platform'}</t>
+          <t>Platform</t>
         </is>
       </c>
     </row>
